--- a/tutoring/charlotte/Charlotte_RAG_tracker.xlsx
+++ b/tutoring/charlotte/Charlotte_RAG_tracker.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Start here" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="RAG tracker" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Worksheets" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Routes" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="364">
   <si>
     <t xml:space="preserve">Summary</t>
   </si>
@@ -133,6 +134,12 @@
     <t xml:space="preserve">About 55 rows. It should take 20 to 30 minutes. You do not need to do any maths to fill it in.</t>
   </si>
   <si>
+    <t xml:space="preserve">Modular unit column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignore this unless you are on the modular route. It says which of the two units the topic sits in.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Example of a filled row</t>
   </si>
   <si>
@@ -148,6 +155,9 @@
     <t xml:space="preserve">Level</t>
   </si>
   <si>
+    <t xml:space="preserve">Modular unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Your rating</t>
   </si>
   <si>
@@ -166,6 +176,9 @@
     <t xml:space="preserve">Foundation</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fine adding, always get stuck dividing</t>
   </si>
   <si>
@@ -223,6 +236,9 @@
     <t xml:space="preserve">Squares, cubes and their roots, index laws for positive and negative powers, product of prime factors, HCF and LCM</t>
   </si>
   <si>
+    <t xml:space="preserve">Units 1 and 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.4H</t>
   </si>
   <si>
@@ -262,6 +278,9 @@
     <t xml:space="preserve">Ratio notation and simplifying, dividing a quantity in a ratio, unitary method, direct proportion, maps and scale diagrams</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.8</t>
   </si>
   <si>
@@ -986,6 +1005,117 @@
   </si>
   <si>
     <t xml:space="preserve">Conditional Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which qualification is this?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two different Edexcel qualifications share the same content. The tracker works for both, but the exam structure and the grading differ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualification code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4MA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4XMAH (Higher cash-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4MA1/1H and 4MA1/2H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4WM1H/01 and 4WM2H/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two papers, each sampling the whole specification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two units, the content split between them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November 2026 dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wed 4 Nov and Fri 6 Nov, both morning, 2 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 raw marks per paper, 200 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 raw marks per unit, converted to 120 UMS per unit, 240 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 5 boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 out of 200 raw in November 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 out of 240 UMS, fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 4 boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 out of 200 raw in November 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 out of 240 UMS, fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The whole qualification is resat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual units can be resat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK and international centres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centres outside the UK only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical. The modular route splits the same content across two units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to tell which one Charlotte is on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The modular qualification is only available to centres outside the UK, so a UK school means the linear 4MA1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask the school for the entry code on her statement of entry. 4MA1 is linear, 4WM1H or 4WM2H is modular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The dates and times are the same either way, so the plan does not change. The grading does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the modular route a raw mark is converted to UMS, so the grade 5 line is fixed at 120 of 240 rather than moving each series.</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1126,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1094,6 +1224,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF162947"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1182,7 +1320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1269,6 +1407,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1587,7 +1733,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">COUNTIFS('RAG tracker'!$E$2:$E$57,$A5)</f>
+        <f aca="false">COUNTIFS('RAG tracker'!$F$2:$F$57,$A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1606,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">COUNTIFS('RAG tracker'!$E$2:$E$57,$A6)</f>
+        <f aca="false">COUNTIFS('RAG tracker'!$F$2:$F$57,$A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1625,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">COUNTIFS('RAG tracker'!$E$2:$E$57,$A7)</f>
+        <f aca="false">COUNTIFS('RAG tracker'!$F$2:$F$57,$A7)</f>
         <v>0</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1644,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">COUNTIFS('RAG tracker'!$E$2:$E$57,"")</f>
+        <f aca="false">COUNTIFS('RAG tracker'!$F$2:$F$57,"")</f>
         <v>56</v>
       </c>
       <c r="C8" s="5"/>
@@ -1724,15 +1870,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1801,49 +1948,63 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>36</v>
       </c>
+      <c r="B11" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="E14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="F14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="G14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="14" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="B15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>47</v>
+      <c r="G15" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1862,1335 +2023,1507 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="14" t="str">
-        <f aca="false">IF($E2="","",IF($E2="R","Full worksheet, taught first",IF($E2="A","Work until 3 right in a row",IF($E2="G","2 question spot check in week 5",""))))</f>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="14" t="str">
+        <f aca="false">IF($F2="","",IF($F2="R","Full worksheet, taught first",IF($F2="A","Work until 3 right in a row",IF($F2="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="14" t="str">
-        <f aca="false">IF($E3="","",IF($E3="R","Full worksheet, taught first",IF($E3="A","Work until 3 right in a row",IF($E3="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="14" t="str">
+        <f aca="false">IF($F3="","",IF($F3="R","Full worksheet, taught first",IF($F3="A","Work until 3 right in a row",IF($F3="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="14" t="str">
-        <f aca="false">IF($E4="","",IF($E4="R","Full worksheet, taught first",IF($E4="A","Work until 3 right in a row",IF($E4="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="14" t="str">
+        <f aca="false">IF($F4="","",IF($F4="R","Full worksheet, taught first",IF($F4="A","Work until 3 right in a row",IF($F4="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="14" t="str">
-        <f aca="false">IF($E5="","",IF($E5="R","Full worksheet, taught first",IF($E5="A","Work until 3 right in a row",IF($E5="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="14" t="str">
+        <f aca="false">IF($F5="","",IF($F5="R","Full worksheet, taught first",IF($F5="A","Work until 3 right in a row",IF($F5="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="14" t="str">
-        <f aca="false">IF($E6="","",IF($E6="R","Full worksheet, taught first",IF($E6="A","Work until 3 right in a row",IF($E6="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="14" t="str">
+        <f aca="false">IF($F6="","",IF($F6="R","Full worksheet, taught first",IF($F6="A","Work until 3 right in a row",IF($F6="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="14" t="str">
-        <f aca="false">IF($E7="","",IF($E7="R","Full worksheet, taught first",IF($E7="A","Work until 3 right in a row",IF($E7="G","2 question spot check in week 5",""))))</f>
+      <c r="I7" s="14" t="str">
+        <f aca="false">IF($F7="","",IF($F7="R","Full worksheet, taught first",IF($F7="A","Work until 3 right in a row",IF($F7="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="14" t="str">
-        <f aca="false">IF($E8="","",IF($E8="R","Full worksheet, taught first",IF($E8="A","Work until 3 right in a row",IF($E8="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="14" t="str">
+        <f aca="false">IF($F8="","",IF($F8="R","Full worksheet, taught first",IF($F8="A","Work until 3 right in a row",IF($F8="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="14" t="str">
-        <f aca="false">IF($E9="","",IF($E9="R","Full worksheet, taught first",IF($E9="A","Work until 3 right in a row",IF($E9="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="14" t="str">
+        <f aca="false">IF($F9="","",IF($F9="R","Full worksheet, taught first",IF($F9="A","Work until 3 right in a row",IF($F9="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="14" t="str">
-        <f aca="false">IF($E10="","",IF($E10="R","Full worksheet, taught first",IF($E10="A","Work until 3 right in a row",IF($E10="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f aca="false">IF($F10="","",IF($F10="R","Full worksheet, taught first",IF($F10="A","Work until 3 right in a row",IF($F10="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="14" t="str">
-        <f aca="false">IF($E11="","",IF($E11="R","Full worksheet, taught first",IF($E11="A","Work until 3 right in a row",IF($E11="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="14" t="str">
+        <f aca="false">IF($F11="","",IF($F11="R","Full worksheet, taught first",IF($F11="A","Work until 3 right in a row",IF($F11="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="14" t="str">
-        <f aca="false">IF($E12="","",IF($E12="R","Full worksheet, taught first",IF($E12="A","Work until 3 right in a row",IF($E12="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="14" t="str">
+        <f aca="false">IF($F12="","",IF($F12="R","Full worksheet, taught first",IF($F12="A","Work until 3 right in a row",IF($F12="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="14" t="str">
-        <f aca="false">IF($E13="","",IF($E13="R","Full worksheet, taught first",IF($E13="A","Work until 3 right in a row",IF($E13="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="14" t="str">
+        <f aca="false">IF($F13="","",IF($F13="R","Full worksheet, taught first",IF($F13="A","Work until 3 right in a row",IF($F13="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="14" t="str">
-        <f aca="false">IF($E14="","",IF($E14="R","Full worksheet, taught first",IF($E14="A","Work until 3 right in a row",IF($E14="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="14" t="str">
+        <f aca="false">IF($F14="","",IF($F14="R","Full worksheet, taught first",IF($F14="A","Work until 3 right in a row",IF($F14="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="14" t="str">
-        <f aca="false">IF($E15="","",IF($E15="R","Full worksheet, taught first",IF($E15="A","Work until 3 right in a row",IF($E15="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="14" t="str">
+        <f aca="false">IF($F15="","",IF($F15="R","Full worksheet, taught first",IF($F15="A","Work until 3 right in a row",IF($F15="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="14" t="str">
-        <f aca="false">IF($E16="","",IF($E16="R","Full worksheet, taught first",IF($E16="A","Work until 3 right in a row",IF($E16="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="14" t="str">
+        <f aca="false">IF($F16="","",IF($F16="R","Full worksheet, taught first",IF($F16="A","Work until 3 right in a row",IF($F16="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="14" t="str">
-        <f aca="false">IF($E17="","",IF($E17="R","Full worksheet, taught first",IF($E17="A","Work until 3 right in a row",IF($E17="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="14" t="str">
+        <f aca="false">IF($F17="","",IF($F17="R","Full worksheet, taught first",IF($F17="A","Work until 3 right in a row",IF($F17="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="14" t="str">
-        <f aca="false">IF($E18="","",IF($E18="R","Full worksheet, taught first",IF($E18="A","Work until 3 right in a row",IF($E18="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="14" t="str">
+        <f aca="false">IF($F18="","",IF($F18="R","Full worksheet, taught first",IF($F18="A","Work until 3 right in a row",IF($F18="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="14" t="str">
-        <f aca="false">IF($E19="","",IF($E19="R","Full worksheet, taught first",IF($E19="A","Work until 3 right in a row",IF($E19="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="14" t="str">
+        <f aca="false">IF($F19="","",IF($F19="R","Full worksheet, taught first",IF($F19="A","Work until 3 right in a row",IF($F19="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="14" t="str">
-        <f aca="false">IF($E20="","",IF($E20="R","Full worksheet, taught first",IF($E20="A","Work until 3 right in a row",IF($E20="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f aca="false">IF($F20="","",IF($F20="R","Full worksheet, taught first",IF($F20="A","Work until 3 right in a row",IF($F20="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H21" s="14" t="str">
-        <f aca="false">IF($E21="","",IF($E21="R","Full worksheet, taught first",IF($E21="A","Work until 3 right in a row",IF($E21="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" s="14" t="str">
+        <f aca="false">IF($F21="","",IF($F21="R","Full worksheet, taught first",IF($F21="A","Work until 3 right in a row",IF($F21="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="14" t="str">
-        <f aca="false">IF($E22="","",IF($E22="R","Full worksheet, taught first",IF($E22="A","Work until 3 right in a row",IF($E22="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="14" t="str">
+        <f aca="false">IF($F22="","",IF($F22="R","Full worksheet, taught first",IF($F22="A","Work until 3 right in a row",IF($F22="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23" s="14" t="str">
-        <f aca="false">IF($E23="","",IF($E23="R","Full worksheet, taught first",IF($E23="A","Work until 3 right in a row",IF($E23="G","2 question spot check in week 5",""))))</f>
+      <c r="I23" s="14" t="str">
+        <f aca="false">IF($F23="","",IF($F23="R","Full worksheet, taught first",IF($F23="A","Work until 3 right in a row",IF($F23="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="14" t="str">
-        <f aca="false">IF($E24="","",IF($E24="R","Full worksheet, taught first",IF($E24="A","Work until 3 right in a row",IF($E24="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="14" t="str">
+        <f aca="false">IF($F24="","",IF($F24="R","Full worksheet, taught first",IF($F24="A","Work until 3 right in a row",IF($F24="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="14" t="str">
-        <f aca="false">IF($E25="","",IF($E25="R","Full worksheet, taught first",IF($E25="A","Work until 3 right in a row",IF($E25="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="14" t="str">
+        <f aca="false">IF($F25="","",IF($F25="R","Full worksheet, taught first",IF($F25="A","Work until 3 right in a row",IF($F25="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" s="14" t="str">
-        <f aca="false">IF($E26="","",IF($E26="R","Full worksheet, taught first",IF($E26="A","Work until 3 right in a row",IF($E26="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="14" t="str">
+        <f aca="false">IF($F26="","",IF($F26="R","Full worksheet, taught first",IF($F26="A","Work until 3 right in a row",IF($F26="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="14" t="str">
-        <f aca="false">IF($E27="","",IF($E27="R","Full worksheet, taught first",IF($E27="A","Work until 3 right in a row",IF($E27="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="14" t="str">
+        <f aca="false">IF($F27="","",IF($F27="R","Full worksheet, taught first",IF($F27="A","Work until 3 right in a row",IF($F27="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H28" s="14" t="str">
-        <f aca="false">IF($E28="","",IF($E28="R","Full worksheet, taught first",IF($E28="A","Work until 3 right in a row",IF($E28="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" s="14" t="str">
+        <f aca="false">IF($F28="","",IF($F28="R","Full worksheet, taught first",IF($F28="A","Work until 3 right in a row",IF($F28="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="14" t="str">
-        <f aca="false">IF($E29="","",IF($E29="R","Full worksheet, taught first",IF($E29="A","Work until 3 right in a row",IF($E29="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="14" t="str">
+        <f aca="false">IF($F29="","",IF($F29="R","Full worksheet, taught first",IF($F29="A","Work until 3 right in a row",IF($F29="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="14" t="str">
-        <f aca="false">IF($E30="","",IF($E30="R","Full worksheet, taught first",IF($E30="A","Work until 3 right in a row",IF($E30="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="14" t="str">
+        <f aca="false">IF($F30="","",IF($F30="R","Full worksheet, taught first",IF($F30="A","Work until 3 right in a row",IF($F30="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="14" t="str">
-        <f aca="false">IF($E31="","",IF($E31="R","Full worksheet, taught first",IF($E31="A","Work until 3 right in a row",IF($E31="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="14" t="str">
+        <f aca="false">IF($F31="","",IF($F31="R","Full worksheet, taught first",IF($F31="A","Work until 3 right in a row",IF($F31="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H32" s="14" t="str">
-        <f aca="false">IF($E32="","",IF($E32="R","Full worksheet, taught first",IF($E32="A","Work until 3 right in a row",IF($E32="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="14" t="str">
+        <f aca="false">IF($F32="","",IF($F32="R","Full worksheet, taught first",IF($F32="A","Work until 3 right in a row",IF($F32="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H33" s="14" t="str">
-        <f aca="false">IF($E33="","",IF($E33="R","Full worksheet, taught first",IF($E33="A","Work until 3 right in a row",IF($E33="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="14" t="str">
+        <f aca="false">IF($F33="","",IF($F33="R","Full worksheet, taught first",IF($F33="A","Work until 3 right in a row",IF($F33="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H34" s="14" t="str">
-        <f aca="false">IF($E34="","",IF($E34="R","Full worksheet, taught first",IF($E34="A","Work until 3 right in a row",IF($E34="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="14" t="str">
+        <f aca="false">IF($F34="","",IF($F34="R","Full worksheet, taught first",IF($F34="A","Work until 3 right in a row",IF($F34="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H35" s="14" t="str">
-        <f aca="false">IF($E35="","",IF($E35="R","Full worksheet, taught first",IF($E35="A","Work until 3 right in a row",IF($E35="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="14" t="str">
+        <f aca="false">IF($F35="","",IF($F35="R","Full worksheet, taught first",IF($F35="A","Work until 3 right in a row",IF($F35="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H36" s="14" t="str">
-        <f aca="false">IF($E36="","",IF($E36="R","Full worksheet, taught first",IF($E36="A","Work until 3 right in a row",IF($E36="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="18"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I36" s="14" t="str">
+        <f aca="false">IF($F36="","",IF($F36="R","Full worksheet, taught first",IF($F36="A","Work until 3 right in a row",IF($F36="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37" s="14" t="str">
-        <f aca="false">IF($E37="","",IF($E37="R","Full worksheet, taught first",IF($E37="A","Work until 3 right in a row",IF($E37="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="18"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" s="14" t="str">
+        <f aca="false">IF($F37="","",IF($F37="R","Full worksheet, taught first",IF($F37="A","Work until 3 right in a row",IF($F37="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H38" s="14" t="str">
-        <f aca="false">IF($E38="","",IF($E38="R","Full worksheet, taught first",IF($E38="A","Work until 3 right in a row",IF($E38="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" s="18"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I38" s="14" t="str">
+        <f aca="false">IF($F38="","",IF($F38="R","Full worksheet, taught first",IF($F38="A","Work until 3 right in a row",IF($F38="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H39" s="14" t="str">
-        <f aca="false">IF($E39="","",IF($E39="R","Full worksheet, taught first",IF($E39="A","Work until 3 right in a row",IF($E39="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="18"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I39" s="14" t="str">
+        <f aca="false">IF($F39="","",IF($F39="R","Full worksheet, taught first",IF($F39="A","Work until 3 right in a row",IF($F39="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H40" s="14" t="str">
-        <f aca="false">IF($E40="","",IF($E40="R","Full worksheet, taught first",IF($E40="A","Work until 3 right in a row",IF($E40="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I40" s="14" t="str">
+        <f aca="false">IF($F40="","",IF($F40="R","Full worksheet, taught first",IF($F40="A","Work until 3 right in a row",IF($F40="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41" s="14" t="str">
-        <f aca="false">IF($E41="","",IF($E41="R","Full worksheet, taught first",IF($E41="A","Work until 3 right in a row",IF($E41="G","2 question spot check in week 5",""))))</f>
+        <v>77</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="14" t="str">
+        <f aca="false">IF($F41="","",IF($F41="R","Full worksheet, taught first",IF($F41="A","Work until 3 right in a row",IF($F41="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H42" s="14" t="str">
-        <f aca="false">IF($E42="","",IF($E42="R","Full worksheet, taught first",IF($E42="A","Work until 3 right in a row",IF($E42="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="18"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I42" s="14" t="str">
+        <f aca="false">IF($F42="","",IF($F42="R","Full worksheet, taught first",IF($F42="A","Work until 3 right in a row",IF($F42="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H43" s="14" t="str">
-        <f aca="false">IF($E43="","",IF($E43="R","Full worksheet, taught first",IF($E43="A","Work until 3 right in a row",IF($E43="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" s="14" t="str">
+        <f aca="false">IF($F43="","",IF($F43="R","Full worksheet, taught first",IF($F43="A","Work until 3 right in a row",IF($F43="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H44" s="14" t="str">
-        <f aca="false">IF($E44="","",IF($E44="R","Full worksheet, taught first",IF($E44="A","Work until 3 right in a row",IF($E44="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" s="18"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="14" t="str">
+        <f aca="false">IF($F44="","",IF($F44="R","Full worksheet, taught first",IF($F44="A","Work until 3 right in a row",IF($F44="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="14" t="str">
-        <f aca="false">IF($E45="","",IF($E45="R","Full worksheet, taught first",IF($E45="A","Work until 3 right in a row",IF($E45="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="18"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I45" s="14" t="str">
+        <f aca="false">IF($F45="","",IF($F45="R","Full worksheet, taught first",IF($F45="A","Work until 3 right in a row",IF($F45="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E46" s="18"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H46" s="14" t="str">
-        <f aca="false">IF($E46="","",IF($E46="R","Full worksheet, taught first",IF($E46="A","Work until 3 right in a row",IF($E46="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="18"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I46" s="14" t="str">
+        <f aca="false">IF($F46="","",IF($F46="R","Full worksheet, taught first",IF($F46="A","Work until 3 right in a row",IF($F46="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H47" s="14" t="str">
-        <f aca="false">IF($E47="","",IF($E47="R","Full worksheet, taught first",IF($E47="A","Work until 3 right in a row",IF($E47="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="18"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I47" s="14" t="str">
+        <f aca="false">IF($F47="","",IF($F47="R","Full worksheet, taught first",IF($F47="A","Work until 3 right in a row",IF($F47="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H48" s="14" t="str">
-        <f aca="false">IF($E48="","",IF($E48="R","Full worksheet, taught first",IF($E48="A","Work until 3 right in a row",IF($E48="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="18"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I48" s="14" t="str">
+        <f aca="false">IF($F48="","",IF($F48="R","Full worksheet, taught first",IF($F48="A","Work until 3 right in a row",IF($F48="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" s="14" t="str">
-        <f aca="false">IF($E49="","",IF($E49="R","Full worksheet, taught first",IF($E49="A","Work until 3 right in a row",IF($E49="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="18"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I49" s="14" t="str">
+        <f aca="false">IF($F49="","",IF($F49="R","Full worksheet, taught first",IF($F49="A","Work until 3 right in a row",IF($F49="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H50" s="14" t="str">
-        <f aca="false">IF($E50="","",IF($E50="R","Full worksheet, taught first",IF($E50="A","Work until 3 right in a row",IF($E50="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="18"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I50" s="14" t="str">
+        <f aca="false">IF($F50="","",IF($F50="R","Full worksheet, taught first",IF($F50="A","Work until 3 right in a row",IF($F50="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H51" s="14" t="str">
-        <f aca="false">IF($E51="","",IF($E51="R","Full worksheet, taught first",IF($E51="A","Work until 3 right in a row",IF($E51="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" s="18"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I51" s="14" t="str">
+        <f aca="false">IF($F51="","",IF($F51="R","Full worksheet, taught first",IF($F51="A","Work until 3 right in a row",IF($F51="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H52" s="14" t="str">
-        <f aca="false">IF($E52="","",IF($E52="R","Full worksheet, taught first",IF($E52="A","Work until 3 right in a row",IF($E52="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F52" s="18"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I52" s="14" t="str">
+        <f aca="false">IF($F52="","",IF($F52="R","Full worksheet, taught first",IF($F52="A","Work until 3 right in a row",IF($F52="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="53" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E53" s="18"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H53" s="14" t="str">
-        <f aca="false">IF($E53="","",IF($E53="R","Full worksheet, taught first",IF($E53="A","Work until 3 right in a row",IF($E53="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="18"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I53" s="14" t="str">
+        <f aca="false">IF($F53="","",IF($F53="R","Full worksheet, taught first",IF($F53="A","Work until 3 right in a row",IF($F53="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H54" s="14" t="str">
-        <f aca="false">IF($E54="","",IF($E54="R","Full worksheet, taught first",IF($E54="A","Work until 3 right in a row",IF($E54="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" s="18"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I54" s="14" t="str">
+        <f aca="false">IF($F54="","",IF($F54="R","Full worksheet, taught first",IF($F54="A","Work until 3 right in a row",IF($F54="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E55" s="18"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="14" t="str">
-        <f aca="false">IF($E55="","",IF($E55="R","Full worksheet, taught first",IF($E55="A","Work until 3 right in a row",IF($E55="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="18"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I55" s="14" t="str">
+        <f aca="false">IF($F55="","",IF($F55="R","Full worksheet, taught first",IF($F55="A","Work until 3 right in a row",IF($F55="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H56" s="14" t="str">
-        <f aca="false">IF($E56="","",IF($E56="R","Full worksheet, taught first",IF($E56="A","Work until 3 right in a row",IF($E56="G","2 question spot check in week 5",""))))</f>
+        <v>49</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" s="18"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I56" s="14" t="str">
+        <f aca="false">IF($F56="","",IF($F56="R","Full worksheet, taught first",IF($F56="A","Work until 3 right in a row",IF($F56="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
     <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H57" s="14" t="str">
-        <f aca="false">IF($E57="","",IF($E57="R","Full worksheet, taught first",IF($E57="A","Work until 3 right in a row",IF($E57="G","2 question spot check in week 5",""))))</f>
+        <v>65</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F57" s="18"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I57" s="14" t="str">
+        <f aca="false">IF($F57="","",IF($F57="R","Full worksheet, taught first",IF($F57="A","Work until 3 right in a row",IF($F57="G","2 question spot check in week 5",""))))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E57">
+  <conditionalFormatting sqref="F2:F57">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -3202,7 +3535,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Enter R, A or G" errorStyle="stop" operator="between" prompt="R = cannot do it, A = shaky, G = confident" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E57" type="list">
+    <dataValidation allowBlank="true" error="Enter R, A or G" errorStyle="stop" operator="between" prompt="R = cannot do it, A = shaky, G = confident" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F57" type="list">
       <formula1>"R,A,G"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3240,70 +3573,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D2" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E2</f>
+        <f aca="false">'RAG tracker'!$F2</f>
         <v>0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J2" s="21"/>
       <c r="K2" s="21"/>
@@ -3311,32 +3644,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E2</f>
+        <f aca="false">'RAG tracker'!$F2</f>
         <v>0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -3344,32 +3677,32 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E2</f>
+        <f aca="false">'RAG tracker'!$F2</f>
         <v>0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J4" s="21"/>
       <c r="K4" s="21"/>
@@ -3377,32 +3710,32 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E3</f>
+        <f aca="false">'RAG tracker'!$F3</f>
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -3410,32 +3743,32 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E4</f>
+        <f aca="false">'RAG tracker'!$F4</f>
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -3443,32 +3776,32 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E5</f>
+        <f aca="false">'RAG tracker'!$F5</f>
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
@@ -3476,32 +3809,32 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E6</f>
+        <f aca="false">'RAG tracker'!$F6</f>
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -3509,32 +3842,32 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E6</f>
+        <f aca="false">'RAG tracker'!$F6</f>
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J9" s="21"/>
       <c r="K9" s="21"/>
@@ -3542,32 +3875,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E6</f>
+        <f aca="false">'RAG tracker'!$F6</f>
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
@@ -3575,32 +3908,32 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E7</f>
+        <f aca="false">'RAG tracker'!$F7</f>
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21"/>
@@ -3608,32 +3941,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E7</f>
+        <f aca="false">'RAG tracker'!$F7</f>
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
@@ -3641,32 +3974,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E8</f>
+        <f aca="false">'RAG tracker'!$F8</f>
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -3674,32 +4007,32 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E9</f>
+        <f aca="false">'RAG tracker'!$F9</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
@@ -3707,32 +4040,32 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E9</f>
+        <f aca="false">'RAG tracker'!$F9</f>
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
@@ -3740,32 +4073,32 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E9</f>
+        <f aca="false">'RAG tracker'!$F9</f>
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
@@ -3773,32 +4106,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E10</f>
+        <f aca="false">'RAG tracker'!$F10</f>
         <v>0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
@@ -3806,32 +4139,32 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E10</f>
+        <f aca="false">'RAG tracker'!$F10</f>
         <v>0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
@@ -3839,32 +4172,32 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E10</f>
+        <f aca="false">'RAG tracker'!$F10</f>
         <v>0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -3872,32 +4205,32 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E10</f>
+        <f aca="false">'RAG tracker'!$F10</f>
         <v>0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
@@ -3905,32 +4238,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E11</f>
+        <f aca="false">'RAG tracker'!$F11</f>
         <v>0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
@@ -3938,32 +4271,32 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D22" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E11</f>
+        <f aca="false">'RAG tracker'!$F11</f>
         <v>0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21"/>
@@ -3971,32 +4304,32 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D23" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E12</f>
+        <f aca="false">'RAG tracker'!$F12</f>
         <v>0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21"/>
@@ -4004,32 +4337,32 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E13</f>
+        <f aca="false">'RAG tracker'!$F13</f>
         <v>0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21"/>
@@ -4037,32 +4370,32 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E14</f>
+        <f aca="false">'RAG tracker'!$F14</f>
         <v>0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
@@ -4070,32 +4403,32 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E14</f>
+        <f aca="false">'RAG tracker'!$F14</f>
         <v>0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
@@ -4103,32 +4436,32 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E14</f>
+        <f aca="false">'RAG tracker'!$F14</f>
         <v>0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
@@ -4136,20 +4469,20 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D28" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E15</f>
+        <f aca="false">'RAG tracker'!$F15</f>
         <v>0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -4161,32 +4494,32 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E16</f>
+        <f aca="false">'RAG tracker'!$F16</f>
         <v>0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -4194,32 +4527,32 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E16</f>
+        <f aca="false">'RAG tracker'!$F16</f>
         <v>0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I30" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
@@ -4227,32 +4560,32 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D31" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E17</f>
+        <f aca="false">'RAG tracker'!$F17</f>
         <v>0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I31" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
@@ -4260,32 +4593,32 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D32" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E17</f>
+        <f aca="false">'RAG tracker'!$F17</f>
         <v>0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -4293,32 +4626,32 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D33" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E17</f>
+        <f aca="false">'RAG tracker'!$F17</f>
         <v>0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
@@ -4326,32 +4659,32 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D34" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E17</f>
+        <f aca="false">'RAG tracker'!$F17</f>
         <v>0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
@@ -4359,32 +4692,32 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E18</f>
+        <f aca="false">'RAG tracker'!$F18</f>
         <v>0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
@@ -4392,32 +4725,32 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E18</f>
+        <f aca="false">'RAG tracker'!$F18</f>
         <v>0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
@@ -4425,32 +4758,32 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E18</f>
+        <f aca="false">'RAG tracker'!$F18</f>
         <v>0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
@@ -4458,32 +4791,32 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E18</f>
+        <f aca="false">'RAG tracker'!$F18</f>
         <v>0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
@@ -4491,32 +4824,32 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D39" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E19</f>
+        <f aca="false">'RAG tracker'!$F19</f>
         <v>0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
@@ -4524,32 +4857,32 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D40" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E19</f>
+        <f aca="false">'RAG tracker'!$F19</f>
         <v>0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -4557,32 +4890,32 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D41" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E19</f>
+        <f aca="false">'RAG tracker'!$F19</f>
         <v>0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -4590,32 +4923,32 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E20</f>
+        <f aca="false">'RAG tracker'!$F20</f>
         <v>0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
@@ -4623,32 +4956,32 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E21</f>
+        <f aca="false">'RAG tracker'!$F21</f>
         <v>0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J43" s="21"/>
       <c r="K43" s="21"/>
@@ -4656,32 +4989,32 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E21</f>
+        <f aca="false">'RAG tracker'!$F21</f>
         <v>0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J44" s="21"/>
       <c r="K44" s="21"/>
@@ -4689,32 +5022,32 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E22</f>
+        <f aca="false">'RAG tracker'!$F22</f>
         <v>0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J45" s="21"/>
       <c r="K45" s="21"/>
@@ -4722,32 +5055,32 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E22</f>
+        <f aca="false">'RAG tracker'!$F22</f>
         <v>0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
@@ -4755,32 +5088,32 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E23</f>
+        <f aca="false">'RAG tracker'!$F23</f>
         <v>0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
@@ -4788,32 +5121,32 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E23</f>
+        <f aca="false">'RAG tracker'!$F23</f>
         <v>0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
@@ -4821,32 +5154,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E24</f>
+        <f aca="false">'RAG tracker'!$F24</f>
         <v>0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J49" s="21"/>
       <c r="K49" s="21"/>
@@ -4854,32 +5187,32 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E24</f>
+        <f aca="false">'RAG tracker'!$F24</f>
         <v>0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I50" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J50" s="21"/>
       <c r="K50" s="21"/>
@@ -4887,32 +5220,32 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E25</f>
+        <f aca="false">'RAG tracker'!$F25</f>
         <v>0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I51" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
@@ -4920,32 +5253,32 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E25</f>
+        <f aca="false">'RAG tracker'!$F25</f>
         <v>0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
@@ -4953,32 +5286,32 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E26</f>
+        <f aca="false">'RAG tracker'!$F26</f>
         <v>0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
@@ -4986,32 +5319,32 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E27</f>
+        <f aca="false">'RAG tracker'!$F27</f>
         <v>0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
@@ -5019,32 +5352,32 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E28</f>
+        <f aca="false">'RAG tracker'!$F28</f>
         <v>0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I55" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J55" s="21"/>
       <c r="K55" s="21"/>
@@ -5052,32 +5385,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D56" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E29</f>
+        <f aca="false">'RAG tracker'!$F29</f>
         <v>0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I56" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J56" s="21"/>
       <c r="K56" s="21"/>
@@ -5085,32 +5418,32 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D57" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E30</f>
+        <f aca="false">'RAG tracker'!$F30</f>
         <v>0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I57" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
@@ -5118,32 +5451,32 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D58" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E30</f>
+        <f aca="false">'RAG tracker'!$F30</f>
         <v>0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I58" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
@@ -5151,32 +5484,32 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E30</f>
+        <f aca="false">'RAG tracker'!$F30</f>
         <v>0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I59" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J59" s="21"/>
       <c r="K59" s="21"/>
@@ -5184,32 +5517,32 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E30</f>
+        <f aca="false">'RAG tracker'!$F30</f>
         <v>0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J60" s="21"/>
       <c r="K60" s="21"/>
@@ -5217,32 +5550,32 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E30</f>
+        <f aca="false">'RAG tracker'!$F30</f>
         <v>0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I61" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
@@ -5250,32 +5583,32 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E31</f>
+        <f aca="false">'RAG tracker'!$F31</f>
         <v>0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I62" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
@@ -5283,32 +5616,32 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E31</f>
+        <f aca="false">'RAG tracker'!$F31</f>
         <v>0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J63" s="21"/>
       <c r="K63" s="21"/>
@@ -5316,32 +5649,32 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D64" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E32</f>
+        <f aca="false">'RAG tracker'!$F32</f>
         <v>0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J64" s="21"/>
       <c r="K64" s="21"/>
@@ -5349,32 +5682,32 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D65" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E32</f>
+        <f aca="false">'RAG tracker'!$F32</f>
         <v>0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J65" s="21"/>
       <c r="K65" s="21"/>
@@ -5382,32 +5715,32 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D66" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E32</f>
+        <f aca="false">'RAG tracker'!$F32</f>
         <v>0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J66" s="21"/>
       <c r="K66" s="21"/>
@@ -5415,32 +5748,32 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D67" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E32</f>
+        <f aca="false">'RAG tracker'!$F32</f>
         <v>0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I67" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J67" s="21"/>
       <c r="K67" s="21"/>
@@ -5448,32 +5781,32 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D68" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E32</f>
+        <f aca="false">'RAG tracker'!$F32</f>
         <v>0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I68" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J68" s="21"/>
       <c r="K68" s="21"/>
@@ -5481,20 +5814,20 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D69" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E33</f>
+        <f aca="false">'RAG tracker'!$F33</f>
         <v>0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -5506,32 +5839,32 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D70" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E34</f>
+        <f aca="false">'RAG tracker'!$F34</f>
         <v>0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J70" s="21"/>
       <c r="K70" s="21"/>
@@ -5539,32 +5872,32 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D71" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E34</f>
+        <f aca="false">'RAG tracker'!$F34</f>
         <v>0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I71" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J71" s="21"/>
       <c r="K71" s="21"/>
@@ -5572,32 +5905,32 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D72" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E35</f>
+        <f aca="false">'RAG tracker'!$F35</f>
         <v>0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I72" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
@@ -5605,32 +5938,32 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D73" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E35</f>
+        <f aca="false">'RAG tracker'!$F35</f>
         <v>0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I73" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J73" s="21"/>
       <c r="K73" s="21"/>
@@ -5638,32 +5971,32 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D74" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E35</f>
+        <f aca="false">'RAG tracker'!$F35</f>
         <v>0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J74" s="21"/>
       <c r="K74" s="21"/>
@@ -5671,32 +6004,32 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D75" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E36</f>
+        <f aca="false">'RAG tracker'!$F36</f>
         <v>0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I75" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J75" s="21"/>
       <c r="K75" s="21"/>
@@ -5704,32 +6037,32 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D76" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E37</f>
+        <f aca="false">'RAG tracker'!$F37</f>
         <v>0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I76" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J76" s="21"/>
       <c r="K76" s="21"/>
@@ -5737,32 +6070,32 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D77" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E37</f>
+        <f aca="false">'RAG tracker'!$F37</f>
         <v>0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I77" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J77" s="21"/>
       <c r="K77" s="21"/>
@@ -5770,32 +6103,32 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D78" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E37</f>
+        <f aca="false">'RAG tracker'!$F37</f>
         <v>0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J78" s="21"/>
       <c r="K78" s="21"/>
@@ -5803,32 +6136,32 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D79" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E37</f>
+        <f aca="false">'RAG tracker'!$F37</f>
         <v>0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I79" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J79" s="21"/>
       <c r="K79" s="21"/>
@@ -5836,32 +6169,32 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D80" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E37</f>
+        <f aca="false">'RAG tracker'!$F37</f>
         <v>0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I80" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J80" s="21"/>
       <c r="K80" s="21"/>
@@ -5869,32 +6202,32 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E38</f>
+        <f aca="false">'RAG tracker'!$F38</f>
         <v>0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I81" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
@@ -5902,32 +6235,32 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D82" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E38</f>
+        <f aca="false">'RAG tracker'!$F38</f>
         <v>0</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I82" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J82" s="21"/>
       <c r="K82" s="21"/>
@@ -5935,32 +6268,32 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D83" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E39</f>
+        <f aca="false">'RAG tracker'!$F39</f>
         <v>0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I83" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
@@ -5968,32 +6301,32 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D84" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E39</f>
+        <f aca="false">'RAG tracker'!$F39</f>
         <v>0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I84" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J84" s="21"/>
       <c r="K84" s="21"/>
@@ -6001,32 +6334,32 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D85" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E40</f>
+        <f aca="false">'RAG tracker'!$F40</f>
         <v>0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I85" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -6034,32 +6367,32 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D86" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E41</f>
+        <f aca="false">'RAG tracker'!$F41</f>
         <v>0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I86" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
@@ -6067,32 +6400,32 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D87" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E42</f>
+        <f aca="false">'RAG tracker'!$F42</f>
         <v>0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I87" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
@@ -6100,32 +6433,32 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D88" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E42</f>
+        <f aca="false">'RAG tracker'!$F42</f>
         <v>0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I88" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
@@ -6133,32 +6466,32 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D89" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E42</f>
+        <f aca="false">'RAG tracker'!$F42</f>
         <v>0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I89" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J89" s="21"/>
       <c r="K89" s="21"/>
@@ -6166,32 +6499,32 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D90" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E43</f>
+        <f aca="false">'RAG tracker'!$F43</f>
         <v>0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I90" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
@@ -6199,32 +6532,32 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D91" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E43</f>
+        <f aca="false">'RAG tracker'!$F43</f>
         <v>0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I91" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21"/>
@@ -6232,32 +6565,32 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D92" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E44</f>
+        <f aca="false">'RAG tracker'!$F44</f>
         <v>0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I92" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J92" s="21"/>
       <c r="K92" s="21"/>
@@ -6265,32 +6598,32 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D93" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E44</f>
+        <f aca="false">'RAG tracker'!$F44</f>
         <v>0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I93" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J93" s="21"/>
       <c r="K93" s="21"/>
@@ -6298,32 +6631,32 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D94" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E44</f>
+        <f aca="false">'RAG tracker'!$F44</f>
         <v>0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I94" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -6331,32 +6664,32 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D95" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E44</f>
+        <f aca="false">'RAG tracker'!$F44</f>
         <v>0</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I95" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
@@ -6364,32 +6697,32 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D96" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E44</f>
+        <f aca="false">'RAG tracker'!$F44</f>
         <v>0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G96" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I96" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
@@ -6397,32 +6730,32 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D97" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E45</f>
+        <f aca="false">'RAG tracker'!$F45</f>
         <v>0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I97" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
@@ -6430,32 +6763,32 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D98" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E46</f>
+        <f aca="false">'RAG tracker'!$F46</f>
         <v>0</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I98" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
@@ -6463,32 +6796,32 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D99" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E46</f>
+        <f aca="false">'RAG tracker'!$F46</f>
         <v>0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I99" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
@@ -6496,32 +6829,32 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D100" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E47</f>
+        <f aca="false">'RAG tracker'!$F47</f>
         <v>0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J100" s="21"/>
       <c r="K100" s="21"/>
@@ -6529,32 +6862,32 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D101" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E48</f>
+        <f aca="false">'RAG tracker'!$F48</f>
         <v>0</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I101" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J101" s="21"/>
       <c r="K101" s="21"/>
@@ -6562,32 +6895,32 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D102" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E48</f>
+        <f aca="false">'RAG tracker'!$F48</f>
         <v>0</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J102" s="21"/>
       <c r="K102" s="21"/>
@@ -6595,32 +6928,32 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D103" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E49</f>
+        <f aca="false">'RAG tracker'!$F49</f>
         <v>0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I103" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
@@ -6628,32 +6961,32 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D104" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E50</f>
+        <f aca="false">'RAG tracker'!$F50</f>
         <v>0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I104" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J104" s="21"/>
       <c r="K104" s="21"/>
@@ -6661,32 +6994,32 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D105" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E50</f>
+        <f aca="false">'RAG tracker'!$F50</f>
         <v>0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I105" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J105" s="21"/>
       <c r="K105" s="21"/>
@@ -6694,32 +7027,32 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D106" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E50</f>
+        <f aca="false">'RAG tracker'!$F50</f>
         <v>0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I106" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
@@ -6727,32 +7060,32 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D107" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E51</f>
+        <f aca="false">'RAG tracker'!$F51</f>
         <v>0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I107" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J107" s="21"/>
       <c r="K107" s="21"/>
@@ -6760,32 +7093,32 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D108" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E51</f>
+        <f aca="false">'RAG tracker'!$F51</f>
         <v>0</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I108" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J108" s="21"/>
       <c r="K108" s="21"/>
@@ -6793,32 +7126,32 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D109" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E52</f>
+        <f aca="false">'RAG tracker'!$F52</f>
         <v>0</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I109" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J109" s="21"/>
       <c r="K109" s="21"/>
@@ -6826,32 +7159,32 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D110" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E52</f>
+        <f aca="false">'RAG tracker'!$F52</f>
         <v>0</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G110" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I110" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J110" s="21"/>
       <c r="K110" s="21"/>
@@ -6859,32 +7192,32 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D111" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E53</f>
+        <f aca="false">'RAG tracker'!$F53</f>
         <v>0</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J111" s="21"/>
       <c r="K111" s="21"/>
@@ -6892,32 +7225,32 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D112" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E53</f>
+        <f aca="false">'RAG tracker'!$F53</f>
         <v>0</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I112" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J112" s="21"/>
       <c r="K112" s="21"/>
@@ -6925,32 +7258,32 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D113" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E54</f>
+        <f aca="false">'RAG tracker'!$F54</f>
         <v>0</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I113" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
@@ -6958,32 +7291,32 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D114" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E54</f>
+        <f aca="false">'RAG tracker'!$F54</f>
         <v>0</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I114" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J114" s="21"/>
       <c r="K114" s="21"/>
@@ -6991,32 +7324,32 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D115" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E55</f>
+        <f aca="false">'RAG tracker'!$F55</f>
         <v>0</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I115" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J115" s="21"/>
       <c r="K115" s="21"/>
@@ -7024,32 +7357,32 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D116" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E56</f>
+        <f aca="false">'RAG tracker'!$F56</f>
         <v>0</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F116" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I116" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
@@ -7057,32 +7390,32 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D117" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E56</f>
+        <f aca="false">'RAG tracker'!$F56</f>
         <v>0</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I117" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
@@ -7090,32 +7423,32 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D118" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E56</f>
+        <f aca="false">'RAG tracker'!$F56</f>
         <v>0</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
@@ -7123,32 +7456,32 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D119" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E57</f>
+        <f aca="false">'RAG tracker'!$F57</f>
         <v>0</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I119" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
@@ -7156,32 +7489,32 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D120" s="5" t="n">
-        <f aca="false">'RAG tracker'!$E57</f>
+        <f aca="false">'RAG tracker'!$F57</f>
         <v>0</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F120" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J120" s="21"/>
       <c r="K120" s="21"/>
@@ -7560,4 +7893,182 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/tutoring/charlotte/Charlotte_RAG_tracker.xlsx
+++ b/tutoring/charlotte/Charlotte_RAG_tracker.xlsx
@@ -200,7 +200,7 @@
     <t xml:space="preserve">Core</t>
   </si>
   <si>
-    <t xml:space="preserve">Equivalent fractions and simplifying, mixed numbers, all four operations, a fraction of a quantity, converting to decimals and percentages</t>
+    <t xml:space="preserve">Equivalent fractions and simplifying, mixed numbers, common denominators, all four operations, reciprocals, a fraction of a quantity, writing one number as a fraction of another, converting to decimals and percentages</t>
   </si>
   <si>
     <t xml:space="preserve">1.3</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">Percentages</t>
   </si>
   <si>
-    <t xml:space="preserve">Percentage of a quantity, one number as a percentage of another, increase and decrease, reverse percentages, compound interest and depreciation, repeated percentage change</t>
+    <t xml:space="preserve">Converting between percentages, fractions and decimals, percentage of a quantity, one number as a percentage of another, percentage multipliers, increase and decrease, reverse percentages, compound interest and depreciation, repeated percentage change</t>
   </si>
   <si>
     <t xml:space="preserve">1.7</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">Ratio and proportion</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio notation and simplifying, dividing a quantity in a ratio, unitary method, direct proportion, maps and scale diagrams</t>
+    <t xml:space="preserve">Ratio notation, simplifying and the form 1 : n, links between ratio and fractions, dividing a quantity in a ratio, unitary method, direct proportion, maps and scale diagrams</t>
   </si>
   <si>
     <t xml:space="preserve">Unit 2</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">Degree of accuracy</t>
   </si>
   <si>
-    <t xml:space="preserve">Rounding to decimal places and significant figures, estimating by rounding to 1 significant figure</t>
+    <t xml:space="preserve">Rounding integers to a given power of 10, rounding to decimal places and significant figures, estimating by rounding to 1 significant figure</t>
   </si>
   <si>
     <t xml:space="preserve">1.8H</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Inequalities</t>
   </si>
   <si>
-    <t xml:space="preserve">Inequality symbols, number lines, solving linear inequalities, shading regions on a graph</t>
+    <t xml:space="preserve">Inequality symbols including double ended, open and closed intervals on a number line, solving linear inequalities, shading and identifying regions on a graph</t>
   </si>
   <si>
     <t xml:space="preserve">2.8H</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">Harder graphs</t>
   </si>
   <si>
-    <t xml:space="preserve">Cubic, reciprocal, exponential and trigonometric graphs, transformations of y = f(x), gradients of curves by tangent, circle equations</t>
+    <t xml:space="preserve">Cubic, reciprocal, exponential and trigonometric graphs, transformations of y = f(x), gradients of curves by drawing a tangent, where two graphs intersect and how that solves an equation, circle equations</t>
   </si>
   <si>
     <t xml:space="preserve">3.4</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">Probability</t>
   </si>
   <si>
-    <t xml:space="preserve">Probability language and scale, sample space, listing outcomes, Venn diagrams, complement, addition rule for mutually exclusive events, expected frequency</t>
+    <t xml:space="preserve">Probability language and scale, sample space, listing outcomes, Venn diagrams, complement, addition rule for mutually exclusive events, estimating probability from collected data, expected frequency</t>
   </si>
   <si>
     <t xml:space="preserve">6.3H</t>
